--- a/CPRD Raw Analysis/Results/Output_visits_Raw-Boot.xlsx
+++ b/CPRD Raw Analysis/Results/Output_visits_Raw-Boot.xlsx
@@ -376,13 +376,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>27.469</v>
+        <v>22.901</v>
       </c>
       <c r="B2">
-        <v>27.153</v>
+        <v>22.556</v>
       </c>
       <c r="C2">
-        <v>27.786</v>
+        <v>23.26</v>
       </c>
     </row>
   </sheetData>
@@ -414,13 +414,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>27.902</v>
+        <v>23.543</v>
       </c>
       <c r="B2">
-        <v>27.595</v>
+        <v>23.194</v>
       </c>
       <c r="C2">
-        <v>28.212</v>
+        <v>23.889</v>
       </c>
     </row>
   </sheetData>
@@ -452,13 +452,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>29.689</v>
+        <v>28.175</v>
       </c>
       <c r="B2">
-        <v>29.375</v>
+        <v>27.771</v>
       </c>
       <c r="C2">
-        <v>30.012</v>
+        <v>28.582</v>
       </c>
     </row>
   </sheetData>
@@ -490,13 +490,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>29.942</v>
+        <v>28.483</v>
       </c>
       <c r="B2">
-        <v>29.622</v>
+        <v>28.059</v>
       </c>
       <c r="C2">
-        <v>30.266</v>
+        <v>28.875</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_visits_Raw-Boot.xlsx
+++ b/CPRD Raw Analysis/Results/Output_visits_Raw-Boot.xlsx
@@ -376,13 +376,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>19.358</v>
+        <v>21.139</v>
       </c>
       <c r="B2">
-        <v>19.031</v>
+        <v>20.856</v>
       </c>
       <c r="C2">
-        <v>19.699</v>
+        <v>21.434</v>
       </c>
     </row>
   </sheetData>
@@ -414,13 +414,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>20.277</v>
+        <v>21.799</v>
       </c>
       <c r="B2">
-        <v>19.95</v>
+        <v>21.5</v>
       </c>
       <c r="C2">
-        <v>20.615</v>
+        <v>22.086</v>
       </c>
     </row>
   </sheetData>
@@ -452,13 +452,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>23.504</v>
+        <v>27.575</v>
       </c>
       <c r="B2">
-        <v>23.112</v>
+        <v>27.2</v>
       </c>
       <c r="C2">
-        <v>23.894</v>
+        <v>27.964</v>
       </c>
     </row>
   </sheetData>
@@ -490,13 +490,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>24.34</v>
+        <v>27.895</v>
       </c>
       <c r="B2">
-        <v>23.915</v>
+        <v>27.525</v>
       </c>
       <c r="C2">
-        <v>24.754</v>
+        <v>28.276</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_visits_Raw-Boot.xlsx
+++ b/CPRD Raw Analysis/Results/Output_visits_Raw-Boot.xlsx
@@ -376,13 +376,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>21.139</v>
+        <v>47.092</v>
       </c>
       <c r="B2">
-        <v>20.856</v>
+        <v>46.476</v>
       </c>
       <c r="C2">
-        <v>21.434</v>
+        <v>47.708</v>
       </c>
     </row>
   </sheetData>
@@ -414,13 +414,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>21.799</v>
+        <v>29.836</v>
       </c>
       <c r="B2">
-        <v>21.5</v>
+        <v>29.388</v>
       </c>
       <c r="C2">
-        <v>22.086</v>
+        <v>30.264</v>
       </c>
     </row>
   </sheetData>
@@ -452,13 +452,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>27.575</v>
+        <v>60.658</v>
       </c>
       <c r="B2">
-        <v>27.2</v>
+        <v>59.802</v>
       </c>
       <c r="C2">
-        <v>27.964</v>
+        <v>61.507</v>
       </c>
     </row>
   </sheetData>
@@ -490,13 +490,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>27.895</v>
+        <v>38.287</v>
       </c>
       <c r="B2">
-        <v>27.525</v>
+        <v>37.695</v>
       </c>
       <c r="C2">
-        <v>28.276</v>
+        <v>38.871</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_visits_Raw-Boot.xlsx
+++ b/CPRD Raw Analysis/Results/Output_visits_Raw-Boot.xlsx
@@ -376,13 +376,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>47.092</v>
+        <v>21.139</v>
       </c>
       <c r="B2">
-        <v>46.476</v>
+        <v>20.856</v>
       </c>
       <c r="C2">
-        <v>47.708</v>
+        <v>21.434</v>
       </c>
     </row>
   </sheetData>
@@ -452,13 +452,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>60.658</v>
+        <v>27.575</v>
       </c>
       <c r="B2">
-        <v>59.802</v>
+        <v>27.2</v>
       </c>
       <c r="C2">
-        <v>61.507</v>
+        <v>27.964</v>
       </c>
     </row>
   </sheetData>
@@ -490,13 +490,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>38.287</v>
+        <v>27.895</v>
       </c>
       <c r="B2">
-        <v>37.695</v>
+        <v>27.525</v>
       </c>
       <c r="C2">
-        <v>38.871</v>
+        <v>28.276</v>
       </c>
     </row>
   </sheetData>
